--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697045</v>
+        <v>131697046</v>
       </c>
       <c r="B6" t="n">
         <v>57898</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511110</v>
+        <v>511115</v>
       </c>
       <c r="R6" t="n">
-        <v>6989836</v>
+        <v>6989841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka en gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1252,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697046</v>
+        <v>131697045</v>
       </c>
       <c r="B7" t="n">
         <v>57898</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511115</v>
+        <v>511110</v>
       </c>
       <c r="R7" t="n">
-        <v>6989841</v>
+        <v>6989836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, enstaka en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697057</v>
       </c>
       <c r="B2" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131697075</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>131697052</v>
       </c>
       <c r="B4" t="n">
-        <v>57739</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131697073</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131697046</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131697045</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131697072</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>131697074</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697057</v>
       </c>
       <c r="B2" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131697075</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>131697052</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131697073</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697046</v>
+        <v>131697045</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511115</v>
+        <v>511110</v>
       </c>
       <c r="R6" t="n">
-        <v>6989841</v>
+        <v>6989836</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, enstaka en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697045</v>
+        <v>131697046</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511110</v>
+        <v>511115</v>
       </c>
       <c r="R7" t="n">
-        <v>6989836</v>
+        <v>6989841</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka en gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,7 +1390,7 @@
         <v>131697072</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>131697074</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131697045</v>
+        <v>131697046</v>
       </c>
       <c r="B6" t="n">
         <v>57902</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511110</v>
+        <v>511115</v>
       </c>
       <c r="R6" t="n">
-        <v>6989836</v>
+        <v>6989841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka en gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1252,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131697046</v>
+        <v>131697045</v>
       </c>
       <c r="B7" t="n">
         <v>57902</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511115</v>
+        <v>511110</v>
       </c>
       <c r="R7" t="n">
-        <v>6989841</v>
+        <v>6989836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, enstaka en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697057</v>
       </c>
       <c r="B2" t="n">
-        <v>80397</v>
+        <v>80399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131697075</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>131697052</v>
       </c>
       <c r="B4" t="n">
-        <v>57743</v>
+        <v>57745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131697073</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131697046</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131697045</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131697072</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>131697074</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697057</v>
       </c>
       <c r="B2" t="n">
-        <v>80399</v>
+        <v>80402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131697075</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>131697052</v>
       </c>
       <c r="B4" t="n">
-        <v>57745</v>
+        <v>57748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131697073</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131697046</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131697045</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131697072</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>131697074</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697057</v>
       </c>
       <c r="B2" t="n">
-        <v>80402</v>
+        <v>80407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131697075</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>131697052</v>
       </c>
       <c r="B4" t="n">
-        <v>57748</v>
+        <v>57753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131697073</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131697046</v>
       </c>
       <c r="B6" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131697045</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131697072</v>
       </c>
       <c r="B8" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>131697074</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 62997-2025 artfynd.xlsx
+++ b/artfynd/A 62997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131697057</v>
       </c>
       <c r="B2" t="n">
-        <v>80407</v>
+        <v>80409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131697075</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>131697052</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>57755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>131697073</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>131697046</v>
       </c>
       <c r="B6" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131697045</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131697072</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>131697074</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
